--- a/artfynd/A 57058-2024 artfynd.xlsx
+++ b/artfynd/A 57058-2024 artfynd.xlsx
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75706261</v>
+        <v>112340376</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmyrbäcken, Ås lm</t>
+          <t>Eldsjömyran, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586972.9622609748</v>
+        <v>587032</v>
       </c>
       <c r="R2" t="n">
-        <v>7105734.054613349</v>
+        <v>7105872</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +757,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 57058-2024 artfynd.xlsx
+++ b/artfynd/A 57058-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,8 +778,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112340376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>